--- a/data/merged/2026-08-31/MERGED_FR_Mite-Vacuum_2026-08-31.xlsx
+++ b/data/merged/2026-08-31/MERGED_FR_Mite-Vacuum_2026-08-31.xlsx
@@ -2765,13 +2765,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2809,13 +2809,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3029,13 +3029,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3073,13 +3073,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3117,13 +3117,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3161,13 +3161,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3205,13 +3205,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3293,13 +3293,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3337,13 +3337,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3513,13 +3513,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3607,7 +3607,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3651,7 +3651,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3668,50 +3668,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId31" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="32" name="Product 32">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId32" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4053,7 +4009,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR33"/>
+  <dimension ref="A1:BR32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -5530,7 +5486,7 @@
       <c r="B12" s="13"/>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>B0DWJQ9GFY</t>
+          <t>B0DX1WQJWN</t>
         </is>
       </c>
       <c r="D12" s="14"/>
@@ -5543,23 +5499,23 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>Hocomay Aspirateur sans fil avec lumière UV-C, aspirateur à main 16 kPa avec écran LED, filtre HEPA, ultrasons, aspirateur de</t>
+          <t>Bear Aspirateur anti-acariens matelas, 15 kpa, 35000 tr/min, UV-C, punaises de lit, 99,9 % bactéries, allergènes, 4 m</t>
         </is>
       </c>
       <c r="I12" s="14"/>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0DWJQ9GFY?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0DX1WQJWN?psc=1</t>
         </is>
       </c>
       <c r="K12" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61bbwwWUftL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61nZHmsIS5L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>B0DWJQ9GFY</t>
+          <t>B0DX1WQJWN</t>
         </is>
       </c>
       <c r="M12" s="1"/>
@@ -5580,11 +5536,11 @@
       <c r="AB12"/>
       <c r="AC12"/>
       <c r="AD12" s="19">
-        <v>2</v>
+        <v>142</v>
       </c>
       <c r="AE12"/>
       <c r="AF12" s="20">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="AG12" s="21">
         <v>0</v>
@@ -5636,7 +5592,7 @@
       <c r="B13" s="13"/>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>B0DX1WQJWN</t>
+          <t>B0F6XNKG8M</t>
         </is>
       </c>
       <c r="D13" s="14"/>
@@ -5649,23 +5605,23 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>Bear Aspirateur anti-acariens matelas, 15 kpa, 35000 tr/min, UV-C, punaises de lit, 99,9 % bactéries, allergènes, 4 m</t>
+          <t>Tiazhan Aspirateur Matelas Anti Acariens, Lumière UV-C et 400 WsÉlimine 99,9% | Air Chaud à 60 °C, Filtre HEPA et Dépoussiér</t>
         </is>
       </c>
       <c r="I13" s="14"/>
       <c r="J13" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0DX1WQJWN?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0F6XNKG8M?psc=1</t>
         </is>
       </c>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61nZHmsIS5L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71iADJb-ECL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L13" s="14" t="inlineStr">
         <is>
-          <t>B0DX1WQJWN</t>
+          <t>B0F6XNKG8M</t>
         </is>
       </c>
       <c r="M13" s="1"/>
@@ -5686,11 +5642,11 @@
       <c r="AB13"/>
       <c r="AC13"/>
       <c r="AD13" s="19">
-        <v>142</v>
+        <v>9</v>
       </c>
       <c r="AE13"/>
       <c r="AF13" s="20">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="AG13" s="21">
         <v>0</v>
@@ -5742,7 +5698,7 @@
       <c r="B14" s="13"/>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>B0F6XNKG8M</t>
+          <t>B0F9NJM4V9</t>
         </is>
       </c>
       <c r="D14" s="14"/>
@@ -5755,23 +5711,23 @@
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>Tiazhan Aspirateur Matelas Anti Acariens, Lumière UV-C et 400 WsÉlimine 99,9% | Air Chaud à 60 °C, Filtre HEPA et Dépoussiér</t>
+          <t>Liwankaqi Aspirateur anti-acariens pour matelas, avec UV C et ultrasons, aspiration 8 KPa, sans fil, anti-allergène, pour lit</t>
         </is>
       </c>
       <c r="I14" s="14"/>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0F6XNKG8M?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0F9NJM4V9?psc=1</t>
         </is>
       </c>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71iADJb-ECL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>B0F6XNKG8M</t>
+          <t>B0F9NJM4V9</t>
         </is>
       </c>
       <c r="M14" s="1"/>
@@ -5792,11 +5748,11 @@
       <c r="AB14"/>
       <c r="AC14"/>
       <c r="AD14" s="19">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AE14"/>
       <c r="AF14" s="20">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="AG14" s="21">
         <v>0</v>
@@ -5848,7 +5804,7 @@
       <c r="B15" s="13"/>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>B0F9NJM4V9</t>
+          <t>B0FDWVV95V</t>
         </is>
       </c>
       <c r="D15" s="14"/>
@@ -5861,23 +5817,23 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>Liwankaqi Aspirateur anti-acariens pour matelas, avec UV C et ultrasons, aspiration 8 KPa, sans fil, anti-allergène, pour lit</t>
+          <t>JIGOO T600 Aspirateur anti-acariens/Floral Delight (huile essentielle végétale)</t>
         </is>
       </c>
       <c r="I15" s="14"/>
       <c r="J15" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0F9NJM4V9?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FDWVV95V?psc=1</t>
         </is>
       </c>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L15" s="14" t="inlineStr">
         <is>
-          <t>B0F9NJM4V9</t>
+          <t>B0FDWVV95V</t>
         </is>
       </c>
       <c r="M15" s="1"/>
@@ -5898,11 +5854,11 @@
       <c r="AB15"/>
       <c r="AC15"/>
       <c r="AD15" s="19">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AE15"/>
       <c r="AF15" s="20">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="AG15" s="21">
         <v>0</v>
@@ -5954,7 +5910,7 @@
       <c r="B16" s="13"/>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>B0FDWVV95V</t>
+          <t>B0FN3V6RFQ</t>
         </is>
       </c>
       <c r="D16" s="14"/>
@@ -5967,23 +5923,23 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>JIGOO T600 Aspirateur anti-acariens/Floral Delight (huile essentielle végétale)</t>
+          <t>Minthouz Aspirateur Anti-acariens</t>
         </is>
       </c>
       <c r="I16" s="14"/>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FDWVV95V?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FN3V6RFQ?psc=1</t>
         </is>
       </c>
       <c r="K16" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71YynWtKuIL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>B0FDWVV95V</t>
+          <t>B0FN3V6RFQ</t>
         </is>
       </c>
       <c r="M16" s="1"/>
@@ -6004,11 +5960,11 @@
       <c r="AB16"/>
       <c r="AC16"/>
       <c r="AD16" s="19">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="AE16"/>
       <c r="AF16" s="20">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AG16" s="21">
         <v>0</v>
@@ -6060,7 +6016,7 @@
       <c r="B17" s="13"/>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>B0FN3V6RFQ</t>
+          <t>B0FVS559GZ</t>
         </is>
       </c>
       <c r="D17" s="14"/>
@@ -6073,23 +6029,23 @@
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>Minthouz Aspirateur Anti-acariens</t>
+          <t>Yaasier Aspirateur Matelas, Aspirateur Anti-acariens pour Matelas avec lumière UV, Aspirateur à Main avec Filtre Hepa, Elimin</t>
         </is>
       </c>
       <c r="I17" s="14"/>
       <c r="J17" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FN3V6RFQ?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FVS559GZ?psc=1</t>
         </is>
       </c>
       <c r="K17" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71YynWtKuIL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L17" s="14" t="inlineStr">
         <is>
-          <t>B0FN3V6RFQ</t>
+          <t>B0FVS559GZ</t>
         </is>
       </c>
       <c r="M17" s="1"/>
@@ -6110,11 +6066,11 @@
       <c r="AB17"/>
       <c r="AC17"/>
       <c r="AD17" s="19">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AE17"/>
       <c r="AF17" s="20">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="AG17" s="21">
         <v>0</v>
@@ -6166,7 +6122,7 @@
       <c r="B18" s="13"/>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>B0FVS559GZ</t>
+          <t>B0FY1MB1LJ</t>
         </is>
       </c>
       <c r="D18" s="14"/>
@@ -6179,23 +6135,23 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>Yaasier Aspirateur Matelas, Aspirateur Anti-acariens pour Matelas avec lumière UV, Aspirateur à Main avec Filtre Hepa, Elimin</t>
+          <t>KOLERFLO Aspirateur Anti-acariens 3 en 1400WsUV-C + air Chaud 65°C, 16000Pa, 12000 Coups/Min, câble 5m, bac 350ml, élimine</t>
         </is>
       </c>
       <c r="I18" s="14"/>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FVS559GZ?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FY1MB1LJ?psc=1</t>
         </is>
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71JpIWC22rL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>B0FVS559GZ</t>
+          <t>B0FY1MB1LJ</t>
         </is>
       </c>
       <c r="M18" s="1"/>
@@ -6216,11 +6172,11 @@
       <c r="AB18"/>
       <c r="AC18"/>
       <c r="AD18" s="19">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AE18"/>
       <c r="AF18" s="20">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="AG18" s="21">
         <v>0</v>
@@ -6272,7 +6228,7 @@
       <c r="B19" s="13"/>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>B0FY1MB1LJ</t>
+          <t>B0FYM1D13D</t>
         </is>
       </c>
       <c r="D19" s="14"/>
@@ -6285,23 +6241,23 @@
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>KOLERFLO Aspirateur Anti-acariens 3 en 1400WsUV-C + air Chaud 65°C, 16000Pa, 12000 Coups/Min, câble 5m, bac 350ml, élimine</t>
+          <t>Aspirateur Matelas, Aspirateur Anti-acariens pour Matelas avec lumière UV, Aspirateur à Main avec Filtre Hepa, Elimine 99,99%</t>
         </is>
       </c>
       <c r="I19" s="14"/>
       <c r="J19" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FY1MB1LJ?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0FYM1D13D?psc=1</t>
         </is>
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71JpIWC22rL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L19" s="14" t="inlineStr">
         <is>
-          <t>B0FY1MB1LJ</t>
+          <t>B0FYM1D13D</t>
         </is>
       </c>
       <c r="M19" s="1"/>
@@ -6322,11 +6278,11 @@
       <c r="AB19"/>
       <c r="AC19"/>
       <c r="AD19" s="19">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="AE19"/>
       <c r="AF19" s="20">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="AG19" s="21">
         <v>0</v>
@@ -6378,7 +6334,7 @@
       <c r="B20" s="13"/>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>B0FYM1D13D</t>
+          <t>B0G4RSJQVT</t>
         </is>
       </c>
       <c r="D20" s="14"/>
@@ -6391,23 +6347,23 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur Matelas, Aspirateur Anti-acariens pour Matelas avec lumière UV, Aspirateur à Main avec Filtre Hepa, Elimine 99,99%</t>
+          <t>Lubluelu Aspirateur Anti-Acariens pour Matelas, Aspirateur Puissant pour Matelas 3 en 1, 18 kPa Puissance d’Aspiration, Élimi</t>
         </is>
       </c>
       <c r="I20" s="14"/>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0FYM1D13D?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0G4RSJQVT?psc=1</t>
         </is>
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71mJa10XC6L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>B0FYM1D13D</t>
+          <t>B0G4RSJQVT</t>
         </is>
       </c>
       <c r="M20" s="1"/>
@@ -6428,11 +6384,11 @@
       <c r="AB20"/>
       <c r="AC20"/>
       <c r="AD20" s="19">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="AE20"/>
       <c r="AF20" s="20">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="AG20" s="21">
         <v>0</v>
@@ -6484,7 +6440,7 @@
       <c r="B21" s="13"/>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>B0G4RSJQVT</t>
+          <t>B0GF7CNTYL</t>
         </is>
       </c>
       <c r="D21" s="14"/>
@@ -6497,23 +6453,23 @@
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>Lubluelu Aspirateur Anti-Acariens pour Matelas, Aspirateur Puissant pour Matelas 3 en 1, 18 kPa Puissance d’Aspiration, Élimi</t>
+          <t>Aspirateur de Matelas UV-C Ultrasonique pour Lit et CanapésAspirateur sans fil pour housses de couette, matelas, canapés en</t>
         </is>
       </c>
       <c r="I21" s="14"/>
       <c r="J21" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0G4RSJQVT?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GF7CNTYL?psc=1</t>
         </is>
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71mJa10XC6L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71H9bRmoUnL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L21" s="14" t="inlineStr">
         <is>
-          <t>B0G4RSJQVT</t>
+          <t>B0GF7CNTYL</t>
         </is>
       </c>
       <c r="M21" s="1"/>
@@ -6533,13 +6489,9 @@
       <c r="AA21"/>
       <c r="AB21"/>
       <c r="AC21"/>
-      <c r="AD21" s="19">
-        <v>26</v>
-      </c>
+      <c r="AD21" s="19"/>
       <c r="AE21"/>
-      <c r="AF21" s="20">
-        <v>4.6</v>
-      </c>
+      <c r="AF21" s="20"/>
       <c r="AG21" s="21">
         <v>0</v>
       </c>
@@ -6590,7 +6542,7 @@
       <c r="B22" s="13"/>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>B0GF7CNTYL</t>
+          <t>B0GGBLWNRZ</t>
         </is>
       </c>
       <c r="D22" s="14"/>
@@ -6603,23 +6555,23 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur de Matelas UV-C Ultrasonique pour Lit et CanapésAspirateur sans fil pour housses de couette, matelas, canapés en</t>
+          <t>Ubric Aspirateur sans fil anti-acariens, avec filtre HEPA, aspirateur de matelas sans fil pour matelas, canapé, coussin, tapi</t>
         </is>
       </c>
       <c r="I22" s="14"/>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GF7CNTYL?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GGBLWNRZ?psc=1</t>
         </is>
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71H9bRmoUnL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/41xNIs1B-1L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>B0GF7CNTYL</t>
+          <t>B0GGBLWNRZ</t>
         </is>
       </c>
       <c r="M22" s="1"/>
@@ -6639,9 +6591,13 @@
       <c r="AA22"/>
       <c r="AB22"/>
       <c r="AC22"/>
-      <c r="AD22" s="19"/>
+      <c r="AD22" s="19">
+        <v>2</v>
+      </c>
       <c r="AE22"/>
-      <c r="AF22" s="20"/>
+      <c r="AF22" s="20">
+        <v>3</v>
+      </c>
       <c r="AG22" s="21">
         <v>0</v>
       </c>
@@ -6692,7 +6648,7 @@
       <c r="B23" s="13"/>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>B0GGBLWNRZ</t>
+          <t>B0GQSRHH7M</t>
         </is>
       </c>
       <c r="D23" s="14"/>
@@ -6705,23 +6661,23 @@
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>Ubric Aspirateur sans fil anti-acariens, avec filtre HEPA, aspirateur de matelas sans fil pour matelas, canapé, coussin, tapi</t>
+          <t>Resmafn 15KPa Aspirateur Anti Acariens avec UV-C et 5M FilsAspirateur Lit, 60°C Chaleur, Réservoir Amovible 1L avec Filtre,</t>
         </is>
       </c>
       <c r="I23" s="14"/>
       <c r="J23" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GGBLWNRZ?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GQSRHH7M?psc=1</t>
         </is>
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/41xNIs1B-1L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61BzcWHyvIL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>B0GGBLWNRZ</t>
+          <t>B0GQSRHH7M</t>
         </is>
       </c>
       <c r="M23" s="1"/>
@@ -6742,11 +6698,11 @@
       <c r="AB23"/>
       <c r="AC23"/>
       <c r="AD23" s="19">
-        <v>2</v>
+        <v>114</v>
       </c>
       <c r="AE23"/>
       <c r="AF23" s="20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG23" s="21">
         <v>0</v>
@@ -6798,7 +6754,7 @@
       <c r="B24" s="13"/>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>B0GQSRHH7M</t>
+          <t>B0GT17NK5X</t>
         </is>
       </c>
       <c r="D24" s="14"/>
@@ -6811,23 +6767,23 @@
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>Resmafn 15KPa Aspirateur Anti Acariens avec UV-C et 5M FilsAspirateur Lit, 60°C Chaleur, Réservoir Amovible 1L avec Filtre,</t>
+          <t>Aspirateur anti-acariens sans fil pour matelas, avec lumière UV de 253,7 nm, ultrasons et tapotements de rouleau de brosse, a</t>
         </is>
       </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GQSRHH7M?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GT17NK5X?psc=1</t>
         </is>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61BzcWHyvIL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71ZkgBFQnaL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>B0GQSRHH7M</t>
+          <t>B0GT17NK5X</t>
         </is>
       </c>
       <c r="M24" s="1"/>
@@ -6848,11 +6804,11 @@
       <c r="AB24"/>
       <c r="AC24"/>
       <c r="AD24" s="19">
-        <v>114</v>
+        <v>1</v>
       </c>
       <c r="AE24"/>
       <c r="AF24" s="20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG24" s="21">
         <v>0</v>
@@ -6904,7 +6860,7 @@
       <c r="B25" s="13"/>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>B0GT17NK5X</t>
+          <t>B0GTYZLWW3</t>
         </is>
       </c>
       <c r="D25" s="14"/>
@@ -6917,23 +6873,23 @@
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur anti-acariens sans fil pour matelas, avec lumière UV de 253,7 nm, ultrasons et tapotements de rouleau de brosse, a</t>
+          <t>Vehiwell Aspirateur anti-acariens, nettoyeur de matelas 15 kPa avec lumière UV-Cs12 000 coups/min, puissance de 600 W, bac</t>
         </is>
       </c>
       <c r="I25" s="14"/>
       <c r="J25" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GT17NK5X?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GTYZLWW3?psc=1</t>
         </is>
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71ZkgBFQnaL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71RQJ5XzBgL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>B0GT17NK5X</t>
+          <t>B0GTYZLWW3</t>
         </is>
       </c>
       <c r="M25" s="1"/>
@@ -6953,13 +6909,9 @@
       <c r="AA25"/>
       <c r="AB25"/>
       <c r="AC25"/>
-      <c r="AD25" s="19">
-        <v>1</v>
-      </c>
+      <c r="AD25" s="19"/>
       <c r="AE25"/>
-      <c r="AF25" s="20">
-        <v>5</v>
-      </c>
+      <c r="AF25" s="20"/>
       <c r="AG25" s="21">
         <v>0</v>
       </c>
@@ -7010,7 +6962,7 @@
       <c r="B26" s="13"/>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>B0GTYZLWW3</t>
+          <t>B0GWD94VPC</t>
         </is>
       </c>
       <c r="D26" s="14"/>
@@ -7023,23 +6975,23 @@
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>Vehiwell Aspirateur anti-acariens, nettoyeur de matelas 15 kPa avec lumière UV-Cs12 000 coups/min, puissance de 600 W, bac</t>
+          <t>JIGOO Aspirateur Anti-acariens T600 pour Matelas, 700 W, avec lumière UV, 15 kPa, Aspiration des acariens, élimine 99,9%, Aff</t>
         </is>
       </c>
       <c r="I26" s="14"/>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GTYZLWW3?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GWD94VPC?psc=1</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71RQJ5XzBgL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/713CpLpTocL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>B0GTYZLWW3</t>
+          <t>B0GWD94VPC</t>
         </is>
       </c>
       <c r="M26" s="1"/>
@@ -7055,7 +7007,9 @@
       <c r="W26" s="15"/>
       <c r="X26" s="15"/>
       <c r="Y26"/>
-      <c r="Z26" s="4"/>
+      <c r="Z26" s="4">
+        <v>133.32</v>
+      </c>
       <c r="AA26"/>
       <c r="AB26"/>
       <c r="AC26"/>
@@ -7112,7 +7066,7 @@
       <c r="B27" s="13"/>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>B0GWD94VPC</t>
+          <t>B0GWH1FGJB</t>
         </is>
       </c>
       <c r="D27" s="14"/>
@@ -7125,23 +7079,23 @@
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>JIGOO Aspirateur Anti-acariens T600 pour Matelas, 700 W, avec lumière UV, 15 kPa, Aspiration des acariens, élimine 99,9%, Aff</t>
+          <t>Aspirateur anti-acariens 2 en 1 pour matelas, stérilisation à lumière bleue et haute fréquence, puissant nettoyeur de matelas</t>
         </is>
       </c>
       <c r="I27" s="14"/>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GWD94VPC?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GWH1FGJB?psc=1</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/713CpLpTocL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61J8ToT-vJL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>B0GWD94VPC</t>
+          <t>B0GWH1FGJB</t>
         </is>
       </c>
       <c r="M27" s="1"/>
@@ -7157,9 +7111,7 @@
       <c r="W27" s="15"/>
       <c r="X27" s="15"/>
       <c r="Y27"/>
-      <c r="Z27" s="4">
-        <v>133.32</v>
-      </c>
+      <c r="Z27" s="4"/>
       <c r="AA27"/>
       <c r="AB27"/>
       <c r="AC27"/>
@@ -7216,7 +7168,7 @@
       <c r="B28" s="13"/>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>B0GWH1FGJB</t>
+          <t>B0GX1RL47V</t>
         </is>
       </c>
       <c r="D28" s="14"/>
@@ -7229,23 +7181,23 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur anti-acariens 2 en 1 pour matelas, stérilisation à lumière bleue et haute fréquence, puissant nettoyeur de matelas</t>
+          <t>CREATULIZE X1 Aspirateur Matelas Robot sans FilsNavigation Intelligente, Évitement d'obstacles, Lumière UV-C 270 Nm, 14AW,</t>
         </is>
       </c>
       <c r="I28" s="14"/>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GWH1FGJB?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GX1RL47V?psc=1</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61J8ToT-vJL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/710Qt1nLGXL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>B0GWH1FGJB</t>
+          <t>B0GX1RL47V</t>
         </is>
       </c>
       <c r="M28" s="1"/>
@@ -7265,9 +7217,13 @@
       <c r="AA28"/>
       <c r="AB28"/>
       <c r="AC28"/>
-      <c r="AD28" s="19"/>
+      <c r="AD28" s="19">
+        <v>12</v>
+      </c>
       <c r="AE28"/>
-      <c r="AF28" s="20"/>
+      <c r="AF28" s="20">
+        <v>4.4</v>
+      </c>
       <c r="AG28" s="21">
         <v>0</v>
       </c>
@@ -7318,7 +7274,7 @@
       <c r="B29" s="13"/>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>B0GX1RL47V</t>
+          <t>B0GYS43G8G</t>
         </is>
       </c>
       <c r="D29" s="14"/>
@@ -7331,23 +7287,23 @@
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>CREATULIZE X1 Aspirateur Matelas Robot sans FilsNavigation Intelligente, Évitement d'obstacles, Lumière UV-C 270 Nm, 14AW,</t>
+          <t>Aspirateur Matelas, Aspirateur Anti-Acariens, Vibration Haute Fréquence, Filtrage Trois Niveaux, Filtre Lavable, pour Canapés</t>
         </is>
       </c>
       <c r="I29" s="14"/>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GX1RL47V?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0GYS43G8G?psc=1</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/710Qt1nLGXL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51JXrvAAoZL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>B0GX1RL47V</t>
+          <t>B0GYS43G8G</t>
         </is>
       </c>
       <c r="M29" s="1"/>
@@ -7368,11 +7324,11 @@
       <c r="AB29"/>
       <c r="AC29"/>
       <c r="AD29" s="19">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AE29"/>
       <c r="AF29" s="20">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="AG29" s="21">
         <v>0</v>
@@ -7424,7 +7380,7 @@
       <c r="B30" s="13"/>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>B0GYS43G8G</t>
+          <t>B0H1HSF3G6</t>
         </is>
       </c>
       <c r="D30" s="14"/>
@@ -7437,23 +7393,23 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Aspirateur Matelas, Aspirateur Anti-Acariens, Vibration Haute Fréquence, Filtrage Trois Niveaux, Filtre Lavable, pour Canapés</t>
+          <t>Circlio V20 Pro 18kPa Aspirateur Anti Acariens pour Matelas avec Lumière UVsDouble bac à Poussière | Punaise de Lit élimine</t>
         </is>
       </c>
       <c r="I30" s="14"/>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0GYS43G8G?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0H1HSF3G6?psc=1</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51JXrvAAoZL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71bkUyyVyuL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>B0GYS43G8G</t>
+          <t>B0H1HSF3G6</t>
         </is>
       </c>
       <c r="M30" s="1"/>
@@ -7474,11 +7430,11 @@
       <c r="AB30"/>
       <c r="AC30"/>
       <c r="AD30" s="19">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE30"/>
       <c r="AF30" s="20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AG30" s="21">
         <v>0</v>
@@ -7530,7 +7486,7 @@
       <c r="B31" s="13"/>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>B0H1HSF3G6</t>
+          <t>B0H418FY5Y</t>
         </is>
       </c>
       <c r="D31" s="14"/>
@@ -7543,23 +7499,23 @@
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>Circlio V20 Pro 18kPa Aspirateur Anti Acariens pour Matelas avec Lumière UVsDouble bac à Poussière | Punaise de Lit élimine</t>
+          <t>Lubluelu Aspirateur Anti-Acariens 3-en-1 20 kPa avec Lampe UV-CsNettoyage en profondeur des matelas et textiles, élimine 99</t>
         </is>
       </c>
       <c r="I31" s="14"/>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0H1HSF3G6?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0H418FY5Y?psc=1</t>
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71bkUyyVyuL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61InrYvl2-L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>B0H1HSF3G6</t>
+          <t>B0H418FY5Y</t>
         </is>
       </c>
       <c r="M31" s="1"/>
@@ -7580,11 +7536,11 @@
       <c r="AB31"/>
       <c r="AC31"/>
       <c r="AD31" s="19">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="AE31"/>
       <c r="AF31" s="20">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AG31" s="21">
         <v>0</v>
@@ -7636,7 +7592,7 @@
       <c r="B32" s="13"/>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>B0H418FY5Y</t>
+          <t>B0H6F2NPXK</t>
         </is>
       </c>
       <c r="D32" s="14"/>
@@ -7649,13 +7605,13 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Lubluelu Aspirateur Anti-Acariens 3-en-1 20 kPa avec Lampe UV-CsNettoyage en profondeur des matelas et textiles, élimine 99</t>
+          <t>Lubluelu Nettoyeur de matelas 3 en 1 20 kPa, aspirateur anti-acariens avec fonction de frappe et fonction chauffante, aspirat</t>
         </is>
       </c>
       <c r="I32" s="14"/>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.fr/dp/B0H418FY5Y?psc=1</t>
+          <t>https://www.amazon.fr/dp/B0H6F2NPXK?psc=1</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
@@ -7665,7 +7621,7 @@
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>B0H418FY5Y</t>
+          <t>B0H6F2NPXK</t>
         </is>
       </c>
       <c r="M32" s="1"/>
@@ -7686,7 +7642,7 @@
       <c r="AB32"/>
       <c r="AC32"/>
       <c r="AD32" s="19">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="AE32"/>
       <c r="AF32" s="20">
@@ -7734,112 +7690,6 @@
       <c r="BP32"/>
       <c r="BQ32" s="22"/>
       <c r="BR32"/>
-    </row>
-    <row r="33" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="13">
-        <v>32</v>
-      </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="14" t="inlineStr">
-        <is>
-          <t>B0H6F2NPXK</t>
-        </is>
-      </c>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33"/>
-      <c r="G33" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.frundefined</t>
-        </is>
-      </c>
-      <c r="H33" s="14" t="inlineStr">
-        <is>
-          <t>Lubluelu Nettoyeur de matelas 3 en 1 20 kPa, aspirateur anti-acariens avec fonction de frappe et fonction chauffante, aspirat</t>
-        </is>
-      </c>
-      <c r="I33" s="14"/>
-      <c r="J33" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.fr/dp/B0H6F2NPXK?psc=1</t>
-        </is>
-      </c>
-      <c r="K33" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61InrYvl2-L._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L33" s="14" t="inlineStr">
-        <is>
-          <t>B0H6F2NPXK</t>
-        </is>
-      </c>
-      <c r="M33" s="1"/>
-      <c r="N33" s="14"/>
-      <c r="O33" s="15"/>
-      <c r="P33" s="15"/>
-      <c r="Q33" s="16"/>
-      <c r="R33" s="17"/>
-      <c r="S33" s="18"/>
-      <c r="T33" s="15"/>
-      <c r="U33" s="16"/>
-      <c r="V33" s="15"/>
-      <c r="W33" s="15"/>
-      <c r="X33" s="15"/>
-      <c r="Y33"/>
-      <c r="Z33" s="4"/>
-      <c r="AA33"/>
-      <c r="AB33"/>
-      <c r="AC33"/>
-      <c r="AD33" s="19">
-        <v>16</v>
-      </c>
-      <c r="AE33"/>
-      <c r="AF33" s="20">
-        <v>4.6</v>
-      </c>
-      <c r="AG33" s="21">
-        <v>0</v>
-      </c>
-      <c r="AH33"/>
-      <c r="AI33" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ33"/>
-      <c r="AK33" s="1"/>
-      <c r="AL33" s="19"/>
-      <c r="AM33"/>
-      <c r="AN33" s="13"/>
-      <c r="AO33" s="13"/>
-      <c r="AP33"/>
-      <c r="AQ33" s="19"/>
-      <c r="AR33"/>
-      <c r="AS33"/>
-      <c r="AT33"/>
-      <c r="AU33" s="13"/>
-      <c r="AV33" s="14"/>
-      <c r="AW33" s="13"/>
-      <c r="AX33" s="13"/>
-      <c r="AY33" s="13"/>
-      <c r="AZ33" s="13"/>
-      <c r="BA33" s="13"/>
-      <c r="BB33" s="13"/>
-      <c r="BC33" s="13"/>
-      <c r="BD33" s="13"/>
-      <c r="BE33" s="13"/>
-      <c r="BF33" s="13"/>
-      <c r="BG33" s="13"/>
-      <c r="BH33" s="14"/>
-      <c r="BI33"/>
-      <c r="BJ33"/>
-      <c r="BK33" s="22"/>
-      <c r="BL33"/>
-      <c r="BM33" s="22"/>
-      <c r="BN33"/>
-      <c r="BO33" s="22"/>
-      <c r="BP33"/>
-      <c r="BQ33" s="22"/>
-      <c r="BR33"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7895,118 +7745,113 @@
     <hyperlink ref="J11" r:id="rId48" tooltip="https://www.amazon.fr/dp/B0DQPZRS8L?psc=1"/>
     <hyperlink ref="K11" r:id="rId49" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71CuqzO5ULL._AC_UL300_SR300,200_.jpg"/>
     <hyperlink ref="L11" r:id="rId50" tooltip="https://www.amazon.fr/dp/B0DQPZRS8L"/>
-    <hyperlink ref="C12" r:id="rId51" tooltip="https://www.amazon.fr/dp/B0DWJQ9GFY"/>
+    <hyperlink ref="C12" r:id="rId51" tooltip="https://www.amazon.fr/dp/B0DX1WQJWN"/>
     <hyperlink ref="G12" r:id="rId52" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J12" r:id="rId53" tooltip="https://www.amazon.fr/dp/B0DWJQ9GFY?psc=1"/>
-    <hyperlink ref="K12" r:id="rId54" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61bbwwWUftL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L12" r:id="rId55" tooltip="https://www.amazon.fr/dp/B0DWJQ9GFY"/>
-    <hyperlink ref="C13" r:id="rId56" tooltip="https://www.amazon.fr/dp/B0DX1WQJWN"/>
+    <hyperlink ref="J12" r:id="rId53" tooltip="https://www.amazon.fr/dp/B0DX1WQJWN?psc=1"/>
+    <hyperlink ref="K12" r:id="rId54" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61nZHmsIS5L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L12" r:id="rId55" tooltip="https://www.amazon.fr/dp/B0DX1WQJWN"/>
+    <hyperlink ref="C13" r:id="rId56" tooltip="https://www.amazon.fr/dp/B0F6XNKG8M"/>
     <hyperlink ref="G13" r:id="rId57" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J13" r:id="rId58" tooltip="https://www.amazon.fr/dp/B0DX1WQJWN?psc=1"/>
-    <hyperlink ref="K13" r:id="rId59" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61nZHmsIS5L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L13" r:id="rId60" tooltip="https://www.amazon.fr/dp/B0DX1WQJWN"/>
-    <hyperlink ref="C14" r:id="rId61" tooltip="https://www.amazon.fr/dp/B0F6XNKG8M"/>
+    <hyperlink ref="J13" r:id="rId58" tooltip="https://www.amazon.fr/dp/B0F6XNKG8M?psc=1"/>
+    <hyperlink ref="K13" r:id="rId59" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71iADJb-ECL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L13" r:id="rId60" tooltip="https://www.amazon.fr/dp/B0F6XNKG8M"/>
+    <hyperlink ref="C14" r:id="rId61" tooltip="https://www.amazon.fr/dp/B0F9NJM4V9"/>
     <hyperlink ref="G14" r:id="rId62" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J14" r:id="rId63" tooltip="https://www.amazon.fr/dp/B0F6XNKG8M?psc=1"/>
-    <hyperlink ref="K14" r:id="rId64" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71iADJb-ECL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L14" r:id="rId65" tooltip="https://www.amazon.fr/dp/B0F6XNKG8M"/>
-    <hyperlink ref="C15" r:id="rId66" tooltip="https://www.amazon.fr/dp/B0F9NJM4V9"/>
+    <hyperlink ref="J14" r:id="rId63" tooltip="https://www.amazon.fr/dp/B0F9NJM4V9?psc=1"/>
+    <hyperlink ref="K14" r:id="rId64" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L14" r:id="rId65" tooltip="https://www.amazon.fr/dp/B0F9NJM4V9"/>
+    <hyperlink ref="C15" r:id="rId66" tooltip="https://www.amazon.fr/dp/B0FDWVV95V"/>
     <hyperlink ref="G15" r:id="rId67" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J15" r:id="rId68" tooltip="https://www.amazon.fr/dp/B0F9NJM4V9?psc=1"/>
-    <hyperlink ref="K15" r:id="rId69" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61GdOBS8v+L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L15" r:id="rId70" tooltip="https://www.amazon.fr/dp/B0F9NJM4V9"/>
-    <hyperlink ref="C16" r:id="rId71" tooltip="https://www.amazon.fr/dp/B0FDWVV95V"/>
+    <hyperlink ref="J15" r:id="rId68" tooltip="https://www.amazon.fr/dp/B0FDWVV95V?psc=1"/>
+    <hyperlink ref="K15" r:id="rId69" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L15" r:id="rId70" tooltip="https://www.amazon.fr/dp/B0FDWVV95V"/>
+    <hyperlink ref="C16" r:id="rId71" tooltip="https://www.amazon.fr/dp/B0FN3V6RFQ"/>
     <hyperlink ref="G16" r:id="rId72" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J16" r:id="rId73" tooltip="https://www.amazon.fr/dp/B0FDWVV95V?psc=1"/>
-    <hyperlink ref="K16" r:id="rId74" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61tL+-AcL6L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L16" r:id="rId75" tooltip="https://www.amazon.fr/dp/B0FDWVV95V"/>
-    <hyperlink ref="C17" r:id="rId76" tooltip="https://www.amazon.fr/dp/B0FN3V6RFQ"/>
+    <hyperlink ref="J16" r:id="rId73" tooltip="https://www.amazon.fr/dp/B0FN3V6RFQ?psc=1"/>
+    <hyperlink ref="K16" r:id="rId74" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71YynWtKuIL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L16" r:id="rId75" tooltip="https://www.amazon.fr/dp/B0FN3V6RFQ"/>
+    <hyperlink ref="C17" r:id="rId76" tooltip="https://www.amazon.fr/dp/B0FVS559GZ"/>
     <hyperlink ref="G17" r:id="rId77" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J17" r:id="rId78" tooltip="https://www.amazon.fr/dp/B0FN3V6RFQ?psc=1"/>
-    <hyperlink ref="K17" r:id="rId79" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71YynWtKuIL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L17" r:id="rId80" tooltip="https://www.amazon.fr/dp/B0FN3V6RFQ"/>
-    <hyperlink ref="C18" r:id="rId81" tooltip="https://www.amazon.fr/dp/B0FVS559GZ"/>
+    <hyperlink ref="J17" r:id="rId78" tooltip="https://www.amazon.fr/dp/B0FVS559GZ?psc=1"/>
+    <hyperlink ref="K17" r:id="rId79" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L17" r:id="rId80" tooltip="https://www.amazon.fr/dp/B0FVS559GZ"/>
+    <hyperlink ref="C18" r:id="rId81" tooltip="https://www.amazon.fr/dp/B0FY1MB1LJ"/>
     <hyperlink ref="G18" r:id="rId82" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J18" r:id="rId83" tooltip="https://www.amazon.fr/dp/B0FVS559GZ?psc=1"/>
-    <hyperlink ref="K18" r:id="rId84" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L18" r:id="rId85" tooltip="https://www.amazon.fr/dp/B0FVS559GZ"/>
-    <hyperlink ref="C19" r:id="rId86" tooltip="https://www.amazon.fr/dp/B0FY1MB1LJ"/>
+    <hyperlink ref="J18" r:id="rId83" tooltip="https://www.amazon.fr/dp/B0FY1MB1LJ?psc=1"/>
+    <hyperlink ref="K18" r:id="rId84" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71JpIWC22rL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L18" r:id="rId85" tooltip="https://www.amazon.fr/dp/B0FY1MB1LJ"/>
+    <hyperlink ref="C19" r:id="rId86" tooltip="https://www.amazon.fr/dp/B0FYM1D13D"/>
     <hyperlink ref="G19" r:id="rId87" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J19" r:id="rId88" tooltip="https://www.amazon.fr/dp/B0FY1MB1LJ?psc=1"/>
-    <hyperlink ref="K19" r:id="rId89" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71JpIWC22rL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L19" r:id="rId90" tooltip="https://www.amazon.fr/dp/B0FY1MB1LJ"/>
-    <hyperlink ref="C20" r:id="rId91" tooltip="https://www.amazon.fr/dp/B0FYM1D13D"/>
+    <hyperlink ref="J19" r:id="rId88" tooltip="https://www.amazon.fr/dp/B0FYM1D13D?psc=1"/>
+    <hyperlink ref="K19" r:id="rId89" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L19" r:id="rId90" tooltip="https://www.amazon.fr/dp/B0FYM1D13D"/>
+    <hyperlink ref="C20" r:id="rId91" tooltip="https://www.amazon.fr/dp/B0G4RSJQVT"/>
     <hyperlink ref="G20" r:id="rId92" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J20" r:id="rId93" tooltip="https://www.amazon.fr/dp/B0FYM1D13D?psc=1"/>
-    <hyperlink ref="K20" r:id="rId94" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51dJLeDXofL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L20" r:id="rId95" tooltip="https://www.amazon.fr/dp/B0FYM1D13D"/>
-    <hyperlink ref="C21" r:id="rId96" tooltip="https://www.amazon.fr/dp/B0G4RSJQVT"/>
+    <hyperlink ref="J20" r:id="rId93" tooltip="https://www.amazon.fr/dp/B0G4RSJQVT?psc=1"/>
+    <hyperlink ref="K20" r:id="rId94" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71mJa10XC6L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L20" r:id="rId95" tooltip="https://www.amazon.fr/dp/B0G4RSJQVT"/>
+    <hyperlink ref="C21" r:id="rId96" tooltip="https://www.amazon.fr/dp/B0GF7CNTYL"/>
     <hyperlink ref="G21" r:id="rId97" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J21" r:id="rId98" tooltip="https://www.amazon.fr/dp/B0G4RSJQVT?psc=1"/>
-    <hyperlink ref="K21" r:id="rId99" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71mJa10XC6L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L21" r:id="rId100" tooltip="https://www.amazon.fr/dp/B0G4RSJQVT"/>
-    <hyperlink ref="C22" r:id="rId101" tooltip="https://www.amazon.fr/dp/B0GF7CNTYL"/>
+    <hyperlink ref="J21" r:id="rId98" tooltip="https://www.amazon.fr/dp/B0GF7CNTYL?psc=1"/>
+    <hyperlink ref="K21" r:id="rId99" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71H9bRmoUnL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L21" r:id="rId100" tooltip="https://www.amazon.fr/dp/B0GF7CNTYL"/>
+    <hyperlink ref="C22" r:id="rId101" tooltip="https://www.amazon.fr/dp/B0GGBLWNRZ"/>
     <hyperlink ref="G22" r:id="rId102" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J22" r:id="rId103" tooltip="https://www.amazon.fr/dp/B0GF7CNTYL?psc=1"/>
-    <hyperlink ref="K22" r:id="rId104" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71H9bRmoUnL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L22" r:id="rId105" tooltip="https://www.amazon.fr/dp/B0GF7CNTYL"/>
-    <hyperlink ref="C23" r:id="rId106" tooltip="https://www.amazon.fr/dp/B0GGBLWNRZ"/>
+    <hyperlink ref="J22" r:id="rId103" tooltip="https://www.amazon.fr/dp/B0GGBLWNRZ?psc=1"/>
+    <hyperlink ref="K22" r:id="rId104" tooltip="https://images-eu.ssl-images-amazon.com/images/I/41xNIs1B-1L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L22" r:id="rId105" tooltip="https://www.amazon.fr/dp/B0GGBLWNRZ"/>
+    <hyperlink ref="C23" r:id="rId106" tooltip="https://www.amazon.fr/dp/B0GQSRHH7M"/>
     <hyperlink ref="G23" r:id="rId107" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J23" r:id="rId108" tooltip="https://www.amazon.fr/dp/B0GGBLWNRZ?psc=1"/>
-    <hyperlink ref="K23" r:id="rId109" tooltip="https://images-eu.ssl-images-amazon.com/images/I/41xNIs1B-1L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L23" r:id="rId110" tooltip="https://www.amazon.fr/dp/B0GGBLWNRZ"/>
-    <hyperlink ref="C24" r:id="rId111" tooltip="https://www.amazon.fr/dp/B0GQSRHH7M"/>
+    <hyperlink ref="J23" r:id="rId108" tooltip="https://www.amazon.fr/dp/B0GQSRHH7M?psc=1"/>
+    <hyperlink ref="K23" r:id="rId109" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61BzcWHyvIL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L23" r:id="rId110" tooltip="https://www.amazon.fr/dp/B0GQSRHH7M"/>
+    <hyperlink ref="C24" r:id="rId111" tooltip="https://www.amazon.fr/dp/B0GT17NK5X"/>
     <hyperlink ref="G24" r:id="rId112" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J24" r:id="rId113" tooltip="https://www.amazon.fr/dp/B0GQSRHH7M?psc=1"/>
-    <hyperlink ref="K24" r:id="rId114" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61BzcWHyvIL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L24" r:id="rId115" tooltip="https://www.amazon.fr/dp/B0GQSRHH7M"/>
-    <hyperlink ref="C25" r:id="rId116" tooltip="https://www.amazon.fr/dp/B0GT17NK5X"/>
+    <hyperlink ref="J24" r:id="rId113" tooltip="https://www.amazon.fr/dp/B0GT17NK5X?psc=1"/>
+    <hyperlink ref="K24" r:id="rId114" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71ZkgBFQnaL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L24" r:id="rId115" tooltip="https://www.amazon.fr/dp/B0GT17NK5X"/>
+    <hyperlink ref="C25" r:id="rId116" tooltip="https://www.amazon.fr/dp/B0GTYZLWW3"/>
     <hyperlink ref="G25" r:id="rId117" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J25" r:id="rId118" tooltip="https://www.amazon.fr/dp/B0GT17NK5X?psc=1"/>
-    <hyperlink ref="K25" r:id="rId119" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71ZkgBFQnaL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L25" r:id="rId120" tooltip="https://www.amazon.fr/dp/B0GT17NK5X"/>
-    <hyperlink ref="C26" r:id="rId121" tooltip="https://www.amazon.fr/dp/B0GTYZLWW3"/>
+    <hyperlink ref="J25" r:id="rId118" tooltip="https://www.amazon.fr/dp/B0GTYZLWW3?psc=1"/>
+    <hyperlink ref="K25" r:id="rId119" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71RQJ5XzBgL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L25" r:id="rId120" tooltip="https://www.amazon.fr/dp/B0GTYZLWW3"/>
+    <hyperlink ref="C26" r:id="rId121" tooltip="https://www.amazon.fr/dp/B0GWD94VPC"/>
     <hyperlink ref="G26" r:id="rId122" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J26" r:id="rId123" tooltip="https://www.amazon.fr/dp/B0GTYZLWW3?psc=1"/>
-    <hyperlink ref="K26" r:id="rId124" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71RQJ5XzBgL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L26" r:id="rId125" tooltip="https://www.amazon.fr/dp/B0GTYZLWW3"/>
-    <hyperlink ref="C27" r:id="rId126" tooltip="https://www.amazon.fr/dp/B0GWD94VPC"/>
+    <hyperlink ref="J26" r:id="rId123" tooltip="https://www.amazon.fr/dp/B0GWD94VPC?psc=1"/>
+    <hyperlink ref="K26" r:id="rId124" tooltip="https://images-eu.ssl-images-amazon.com/images/I/713CpLpTocL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L26" r:id="rId125" tooltip="https://www.amazon.fr/dp/B0GWD94VPC"/>
+    <hyperlink ref="C27" r:id="rId126" tooltip="https://www.amazon.fr/dp/B0GWH1FGJB"/>
     <hyperlink ref="G27" r:id="rId127" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J27" r:id="rId128" tooltip="https://www.amazon.fr/dp/B0GWD94VPC?psc=1"/>
-    <hyperlink ref="K27" r:id="rId129" tooltip="https://images-eu.ssl-images-amazon.com/images/I/713CpLpTocL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L27" r:id="rId130" tooltip="https://www.amazon.fr/dp/B0GWD94VPC"/>
-    <hyperlink ref="C28" r:id="rId131" tooltip="https://www.amazon.fr/dp/B0GWH1FGJB"/>
+    <hyperlink ref="J27" r:id="rId128" tooltip="https://www.amazon.fr/dp/B0GWH1FGJB?psc=1"/>
+    <hyperlink ref="K27" r:id="rId129" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61J8ToT-vJL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L27" r:id="rId130" tooltip="https://www.amazon.fr/dp/B0GWH1FGJB"/>
+    <hyperlink ref="C28" r:id="rId131" tooltip="https://www.amazon.fr/dp/B0GX1RL47V"/>
     <hyperlink ref="G28" r:id="rId132" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J28" r:id="rId133" tooltip="https://www.amazon.fr/dp/B0GWH1FGJB?psc=1"/>
-    <hyperlink ref="K28" r:id="rId134" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61J8ToT-vJL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L28" r:id="rId135" tooltip="https://www.amazon.fr/dp/B0GWH1FGJB"/>
-    <hyperlink ref="C29" r:id="rId136" tooltip="https://www.amazon.fr/dp/B0GX1RL47V"/>
+    <hyperlink ref="J28" r:id="rId133" tooltip="https://www.amazon.fr/dp/B0GX1RL47V?psc=1"/>
+    <hyperlink ref="K28" r:id="rId134" tooltip="https://images-eu.ssl-images-amazon.com/images/I/710Qt1nLGXL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L28" r:id="rId135" tooltip="https://www.amazon.fr/dp/B0GX1RL47V"/>
+    <hyperlink ref="C29" r:id="rId136" tooltip="https://www.amazon.fr/dp/B0GYS43G8G"/>
     <hyperlink ref="G29" r:id="rId137" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J29" r:id="rId138" tooltip="https://www.amazon.fr/dp/B0GX1RL47V?psc=1"/>
-    <hyperlink ref="K29" r:id="rId139" tooltip="https://images-eu.ssl-images-amazon.com/images/I/710Qt1nLGXL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L29" r:id="rId140" tooltip="https://www.amazon.fr/dp/B0GX1RL47V"/>
-    <hyperlink ref="C30" r:id="rId141" tooltip="https://www.amazon.fr/dp/B0GYS43G8G"/>
+    <hyperlink ref="J29" r:id="rId138" tooltip="https://www.amazon.fr/dp/B0GYS43G8G?psc=1"/>
+    <hyperlink ref="K29" r:id="rId139" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51JXrvAAoZL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L29" r:id="rId140" tooltip="https://www.amazon.fr/dp/B0GYS43G8G"/>
+    <hyperlink ref="C30" r:id="rId141" tooltip="https://www.amazon.fr/dp/B0H1HSF3G6"/>
     <hyperlink ref="G30" r:id="rId142" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J30" r:id="rId143" tooltip="https://www.amazon.fr/dp/B0GYS43G8G?psc=1"/>
-    <hyperlink ref="K30" r:id="rId144" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51JXrvAAoZL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L30" r:id="rId145" tooltip="https://www.amazon.fr/dp/B0GYS43G8G"/>
-    <hyperlink ref="C31" r:id="rId146" tooltip="https://www.amazon.fr/dp/B0H1HSF3G6"/>
+    <hyperlink ref="J30" r:id="rId143" tooltip="https://www.amazon.fr/dp/B0H1HSF3G6?psc=1"/>
+    <hyperlink ref="K30" r:id="rId144" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71bkUyyVyuL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L30" r:id="rId145" tooltip="https://www.amazon.fr/dp/B0H1HSF3G6"/>
+    <hyperlink ref="C31" r:id="rId146" tooltip="https://www.amazon.fr/dp/B0H418FY5Y"/>
     <hyperlink ref="G31" r:id="rId147" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J31" r:id="rId148" tooltip="https://www.amazon.fr/dp/B0H1HSF3G6?psc=1"/>
-    <hyperlink ref="K31" r:id="rId149" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71bkUyyVyuL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L31" r:id="rId150" tooltip="https://www.amazon.fr/dp/B0H1HSF3G6"/>
-    <hyperlink ref="C32" r:id="rId151" tooltip="https://www.amazon.fr/dp/B0H418FY5Y"/>
+    <hyperlink ref="J31" r:id="rId148" tooltip="https://www.amazon.fr/dp/B0H418FY5Y?psc=1"/>
+    <hyperlink ref="K31" r:id="rId149" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61InrYvl2-L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L31" r:id="rId150" tooltip="https://www.amazon.fr/dp/B0H418FY5Y"/>
+    <hyperlink ref="C32" r:id="rId151" tooltip="https://www.amazon.fr/dp/B0H6F2NPXK"/>
     <hyperlink ref="G32" r:id="rId152" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J32" r:id="rId153" tooltip="https://www.amazon.fr/dp/B0H418FY5Y?psc=1"/>
+    <hyperlink ref="J32" r:id="rId153" tooltip="https://www.amazon.fr/dp/B0H6F2NPXK?psc=1"/>
     <hyperlink ref="K32" r:id="rId154" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61InrYvl2-L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L32" r:id="rId155" tooltip="https://www.amazon.fr/dp/B0H418FY5Y"/>
-    <hyperlink ref="C33" r:id="rId156" tooltip="https://www.amazon.fr/dp/B0H6F2NPXK"/>
-    <hyperlink ref="G33" r:id="rId157" tooltip="https://www.amazon.frundefined"/>
-    <hyperlink ref="J33" r:id="rId158" tooltip="https://www.amazon.fr/dp/B0H6F2NPXK?psc=1"/>
-    <hyperlink ref="K33" r:id="rId159" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61InrYvl2-L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L33" r:id="rId160" tooltip="https://www.amazon.fr/dp/B0H6F2NPXK"/>
+    <hyperlink ref="L32" r:id="rId155" tooltip="https://www.amazon.fr/dp/B0H6F2NPXK"/>
   </hyperlinks>
-  <drawing r:id="rId161"/>
+  <drawing r:id="rId156"/>
 </worksheet>
 </file>
 
